--- a/app/download_dir/system_files/обувь_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/обувь_по каждому размеру.xlsx
@@ -1401,7 +1401,7 @@
     <t xml:space="preserve">Материал подошвы</t>
   </si>
   <si>
-    <t xml:space="preserve">Замша</t>
+    <t xml:space="preserve">Натуральная замша</t>
   </si>
   <si>
     <t xml:space="preserve">Термопластичная резина</t>
@@ -3814,7 +3814,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AC1035"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.04"/>
@@ -18737,7 +18737,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B678"/>
-  <sheetFormatPr defaultColWidth="12.15625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="63.59"/>
@@ -24020,7 +24020,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B145"/>
-  <sheetFormatPr defaultColWidth="12.06640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.08203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="53.04"/>
   </cols>
